--- a/data/avito_dupes.xlsx
+++ b/data/avito_dupes.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N122"/>
+  <dimension ref="A1:N124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3540,19 +3540,19 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>0am325025m-av</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
+          <t>Импульсное кольцо распредвала GM 55565480</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>4850</v>
+        <v>950</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>4573121040</v>
+        <v>7260747200</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -3565,19 +3565,19 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>4850</v>
+        <v>890</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
@@ -3586,2216 +3586,2262 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
+          <t>Импульсное кольцо распредвала GM 55565480</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/remkomplekt_prokladok_mehatronika_dsg7_dq200_4573121040</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/impulsnoe_koltso_raspredvala_gm_55565480_7260747200</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
+          <t>55565480</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Импульсное кольцо распредвала GM 55565480</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>8461145133</v>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>Импульсное кольцо распредвала GM 55565480</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/impulsnoe_koltso_raspredvala_gm_55565480_8461145133</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>0AM325587E</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>5850</v>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>4284880578</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>5850</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/gidroakkumulyator_dsg7_dq200_0am_0cw_original_vag_4284880578</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>0AM325587E</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>5850</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>8460910607</v>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>5850</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/gidroakkumulyator_mehatronika_dsg7_dq200_original_8460910607</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>0am325025С</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>4285296851</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/koltso_gidroakkumulyatora_dq200_dsg_7_0am_0cw_4285296851</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>0am325025С</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>8449731691</v>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/koltso_gidroakkumulyatora_mehatronika_dsg7_dq200_8449731691</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>01X301127C</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>4284998704</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>1890</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/bolty_mehatronika_dq200_dsg_7_0am_0cw_4284998704</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>01X301127C</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>8446880709</v>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/bolt_mehatronika_korotkiy_dsg7_dq200_0am_0cw_8446880709</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>02e305045</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра мехатроника DSG6 DQ250</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>4284955885</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>1290</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_dq250_dsg_6_02e305045_4284955885</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>02e305045</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра мехатроника DSG6 DQ250</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>8416684544</v>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>1850</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра мехатроника DSG6 DQ250</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_maslyanogo_filtra_mehatronika_dsg6_dq250_8416684544</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Dq500</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>8416432130</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>1940</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_mehatronika_dsg7_dq500_0bh325183b_8416432130</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Dq500</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>8344886348</v>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>1850</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_mehatronika_dsg7_dq500_0bh325183b_8344886348</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>podshipnik-vilki-6</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>4285328953</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>890</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/podshipnik_vilki_dq200_dsg-7_0am_0cw_6r_4285328953</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>podshipnik-vilki-6</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>8416146322</v>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/podshipnik_vilki_6-y_peredachi_i_zadnego_hoda_dsg7_8416146322</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>plita-filtr-salniki-orig</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 оригинальных</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>6350</v>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>8395189204</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>5950</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 оригинальных</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/usilennaya_plita_filtr_2_originalnyh_8395189204</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>plita-filtr-salniki-orig</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 оригинальных</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>6350</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>8276249624</v>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>6350</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 оригинальных</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/usilennaya_plita_filtr_2_originalnyh_8276249624</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>6350</v>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>8341832438</v>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>6220</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/prokladki_salniki_pylniki_mehatronika_dsg7_8341832438</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>6350</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>8394895937</v>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>6350</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/usilennaya_gidroplita_2_pylnika_2_salnika_8394895937</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>317053TX0C</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A)</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>32500</v>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>8387447350</v>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>29450</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/gidroblok_variatora_jf015e_1.6l_re0f11a_novyy_8387447350</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>317053TX0C</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A)</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>32500</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>8274852389</v>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>32500</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A)</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/gidroblok_variatora_jf015e_1.8l_re0f11a_8274852389</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>DQ500</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>4348814868</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>3490</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>Корпус фильтра DQ500 DSG7</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_dq500_dsg7_4348814868</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>DQ500</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>8387244563</v>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>2250</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_filtr_mehatronika_dsg7_dq500_8387244563</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>02E 305 045</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>2350</v>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>4349172359</v>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>1290</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>Корпус фильтра DSG6 DQ250 02E</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_dsg6_dq250_02e_4349172359</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>02E 305 045</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>2350</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>8386056623</v>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>2350</v>
+      </c>
+      <c r="H100" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_filtr_mehatronika_dsg6_dq250_8386056623</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>0BH325183</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>3850</v>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>4285324155</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>3490</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_dq500_dsg_7_0bh325183_4285324155</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>0BH325183</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>3850</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>8374830282</v>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>3850</v>
+      </c>
+      <c r="H103" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_rebristyy_mehatronika_dsg7_dq500_8374830282</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>0am325025m</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>4573121040</v>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>4850</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (уже из фида)</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/remkomplekt_prokladok_mehatronika_dsg7_dq200_4573121040</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>0am325025m</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="n"/>
+      <c r="C106" s="3" t="n"/>
+      <c r="D106" s="3" t="n">
+        <v>8374524447</v>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>4350</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/remkomplekt_prokladok_mehatronika_dsg7_dq200_8374524447</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>0am325025l</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>4444524662</v>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>1290</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/porshen_vilki_mehatronika_dsg7_dq200_0am0cw_4444524662</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>0am325025l</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>8366848631</v>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="H109" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/porshen_tolkatel_vilki_mehatronika_dsg7_dq200_8366848631</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>0сц</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>7260608738</v>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>Сальник толькателя мехатроника dq200 dsg7</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/salnik_tolkatelya_mehatronika_dq200_dsg7_7260608738</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>0сц</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>8324416978</v>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/originalnyy_salnik_shtoka_mehatronika_dsg7_dq200_8324416978</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>0am325066ad</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Сальник-манжета штока сцепления мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>4124845206</v>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/manzhety_salniki_mehatronika_dsg_7_dq200_0am_0cw_4124845206</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>0am325066ad</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>Сальник-манжета штока сцепления мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>8314644270</v>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>Сальник-манжета штока сцепления мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/salnik-manzheta_shtoka_stsepleniya_mehatronika_dsg7_8314644270</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>0AM325433E</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>4189437762</v>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>9850</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/remkomplekt_mehatronika_dsg_7_dq200_plita_filtr_4189437762</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>0AM325433E</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>8274692951</v>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/filtr_mehatronika_dsg7_dq200_0am325433e_8274692951</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>0am325025r</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Усиленное опорное кольцо толкателя мехатроника</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>4284973404</v>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>690</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/usilennoe_opornoe_koltso_tolkatelya_dsg7_dq200_0am_4284973404</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>0am325025r</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Усиленное опорное кольцо толкателя мехатроника</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>8252362999</v>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="H121" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>Усиленное опорное кольцо толкателя мехатроника</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/usilennoe_opornoe_koltso_tolkatelya_mehatronika_8252362999</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
           <t>0am325025m-av</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="C67" s="3" t="n">
+      <c r="C123" s="2" t="n">
         <v>4850</v>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="D123" s="2" t="n">
+        <v>3965211558</v>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>3850</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/remkomplekt_prokladki_mehatronika_dsg7_dq200_0am_3965211558</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>0am325025m-av</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>4850</v>
+      </c>
+      <c r="D124" s="3" t="n">
         <v>4125283125</v>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>ручное</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="n">
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="n">
         <v>11890</v>
       </c>
-      <c r="H67" s="3" t="n">
+      <c r="H124" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="I67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="3" t="n">
+      <c r="I124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L67" s="3" t="inlineStr">
+      <c r="L124" s="3" t="inlineStr">
         <is>
           <t>снять</t>
         </is>
       </c>
-      <c r="M67" s="3" t="inlineStr">
+      <c r="M124" s="3" t="inlineStr">
         <is>
           <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
         </is>
       </c>
-      <c r="N67" s="3" t="inlineStr">
+      <c r="N124" s="3" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/remkomplekt_prokladki_mehatronika_dsg_7_dq200_0am_4125283125</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>0am325025m-av</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>4850</v>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>3965211558</v>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>3850</v>
-      </c>
-      <c r="H68" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K68" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M68" s="3" t="inlineStr">
-        <is>
-          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
-        </is>
-      </c>
-      <c r="N68" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/remkomplekt_prokladki_mehatronika_dsg7_dq200_0am_3965211558</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>55565480</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Импульсное кольцо распредвала GM 55565480</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="D70" s="2" t="n">
-        <v>7260747200</v>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>890</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>Импульсное кольцо распредвала GM 55565480</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/impulsnoe_koltso_raspredvala_gm_55565480_7260747200</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>55565480</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>Импульсное кольцо распредвала GM 55565480</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>8461145133</v>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="H71" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J71" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K71" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L71" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M71" s="3" t="inlineStr">
-        <is>
-          <t>Импульсное кольцо распредвала GM 55565480</t>
-        </is>
-      </c>
-      <c r="N71" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/impulsnoe_koltso_raspredvala_gm_55565480_8461145133</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>0AM325587E</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="n">
-        <v>5850</v>
-      </c>
-      <c r="D73" s="2" t="n">
-        <v>4284880578</v>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>5850</v>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J73" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="K73" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/gidroakkumulyator_dsg7_dq200_0am_0cw_original_vag_4284880578</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>0AM325587E</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="n">
-        <v>5850</v>
-      </c>
-      <c r="D74" s="3" t="n">
-        <v>8460910607</v>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>5850</v>
-      </c>
-      <c r="H74" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="I74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M74" s="3" t="inlineStr">
-        <is>
-          <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал</t>
-        </is>
-      </c>
-      <c r="N74" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/gidroakkumulyator_mehatronika_dsg7_dq200_original_8460910607</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>0am325025С</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="D76" s="2" t="n">
-        <v>4285296851</v>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>450</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K76" s="2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/koltso_gidroakkumulyatora_dq200_dsg_7_0am_0cw_4285296851</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>0am325025С</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="D77" s="3" t="n">
-        <v>8449731691</v>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="H77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M77" s="3" t="inlineStr">
-        <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="N77" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/koltso_gidroakkumulyatora_mehatronika_dsg7_dq200_8449731691</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>01X301127C</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="D79" s="2" t="n">
-        <v>4284998704</v>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>1890</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K79" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/bolty_mehatronika_dq200_dsg_7_0am_0cw_4284998704</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>01X301127C</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="D80" s="3" t="n">
-        <v>8446880709</v>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="H80" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K80" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M80" s="3" t="inlineStr">
-        <is>
-          <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="N80" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/bolt_mehatronika_korotkiy_dsg7_dq200_0am_0cw_8446880709</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>02e305045</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Корпус масляного фильтра мехатроника DSG6 DQ250</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="n">
-        <v>1850</v>
-      </c>
-      <c r="D82" s="2" t="n">
-        <v>4284955885</v>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>1290</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K82" s="2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_dq250_dsg_6_02e305045_4284955885</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>02e305045</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>Корпус масляного фильтра мехатроника DSG6 DQ250</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="n">
-        <v>1850</v>
-      </c>
-      <c r="D83" s="3" t="n">
-        <v>8416684544</v>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="n">
-        <v>1850</v>
-      </c>
-      <c r="H83" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="I83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K83" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M83" s="3" t="inlineStr">
-        <is>
-          <t>Корпус масляного фильтра мехатроника DSG6 DQ250</t>
-        </is>
-      </c>
-      <c r="N83" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_maslyanogo_filtra_mehatronika_dsg6_dq250_8416684544</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Dq500</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v>1850</v>
-      </c>
-      <c r="D85" s="2" t="n">
-        <v>8416432130</v>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>old</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>1940</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_mehatronika_dsg7_dq500_0bh325183b_8416432130</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>Dq500</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="n">
-        <v>1850</v>
-      </c>
-      <c r="D86" s="3" t="n">
-        <v>8344886348</v>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>1850</v>
-      </c>
-      <c r="H86" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L86" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M86" s="3" t="inlineStr">
-        <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
-        </is>
-      </c>
-      <c r="N86" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_mehatronika_dsg7_dq500_0bh325183b_8344886348</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>podshipnik-vilki-6</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="D88" s="2" t="n">
-        <v>4285328953</v>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>890</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K88" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
-        </is>
-      </c>
-      <c r="N88" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/podshipnik_vilki_dq200_dsg-7_0am_0cw_6r_4285328953</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>podshipnik-vilki-6</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="D89" s="3" t="n">
-        <v>8416146322</v>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L89" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M89" s="3" t="inlineStr">
-        <is>
-          <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
-        </is>
-      </c>
-      <c r="N89" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/podshipnik_vilki_6-y_peredachi_i_zadnego_hoda_dsg7_8416146322</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>plita-filtr-salniki-orig</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="n">
-        <v>6350</v>
-      </c>
-      <c r="D91" s="2" t="n">
-        <v>8395189204</v>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>old</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>5950</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/usilennaya_plita_filtr_2_originalnyh_8395189204</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>plita-filtr-salniki-orig</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="n">
-        <v>6350</v>
-      </c>
-      <c r="D92" s="3" t="n">
-        <v>8276249624</v>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>6350</v>
-      </c>
-      <c r="H92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M92" s="3" t="inlineStr">
-        <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных</t>
-        </is>
-      </c>
-      <c r="N92" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/usilennaya_plita_filtr_2_originalnyh_8276249624</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="n">
-        <v>6350</v>
-      </c>
-      <c r="D94" s="2" t="n">
-        <v>8341832438</v>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>old</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>6220</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>Прокладки + сальники + пыльники мехатроника DSG7</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/prokladki_salniki_pylniki_mehatronika_dsg7_8341832438</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="n">
-        <v>6350</v>
-      </c>
-      <c r="D95" s="3" t="n">
-        <v>8394895937</v>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>6350</v>
-      </c>
-      <c r="H95" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M95" s="3" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
-        </is>
-      </c>
-      <c r="N95" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/usilennaya_gidroplita_2_pylnika_2_salnika_8394895937</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>317053TX0C</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A)</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v>32500</v>
-      </c>
-      <c r="D97" s="2" t="n">
-        <v>8387447350</v>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>old</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>29450</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/gidroblok_variatora_jf015e_1.6l_re0f11a_novyy_8387447350</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>317053TX0C</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A)</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="n">
-        <v>32500</v>
-      </c>
-      <c r="D98" s="3" t="n">
-        <v>8274852389</v>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="n">
-        <v>32500</v>
-      </c>
-      <c r="H98" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L98" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M98" s="3" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A)</t>
-        </is>
-      </c>
-      <c r="N98" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/gidroblok_variatora_jf015e_1.8l_re0f11a_8274852389</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>DQ500</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="n">
-        <v>2250</v>
-      </c>
-      <c r="D100" s="2" t="n">
-        <v>4348814868</v>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>3490</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L100" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t>Корпус фильтра DQ500 DSG7</t>
-        </is>
-      </c>
-      <c r="N100" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_dq500_dsg7_4348814868</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>DQ500</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="n">
-        <v>2250</v>
-      </c>
-      <c r="D101" s="3" t="n">
-        <v>8387244563</v>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="n">
-        <v>2250</v>
-      </c>
-      <c r="H101" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="I101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L101" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M101" s="3" t="inlineStr">
-        <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500</t>
-        </is>
-      </c>
-      <c r="N101" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_filtr_mehatronika_dsg7_dq500_8387244563</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>02E 305 045</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="n">
-        <v>2350</v>
-      </c>
-      <c r="D103" s="2" t="n">
-        <v>4349172359</v>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>1290</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>Корпус фильтра DSG6 DQ250 02E</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_dsg6_dq250_02e_4349172359</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>02E 305 045</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="n">
-        <v>2350</v>
-      </c>
-      <c r="D104" s="3" t="n">
-        <v>8386056623</v>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="n">
-        <v>2350</v>
-      </c>
-      <c r="H104" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K104" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L104" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M104" s="3" t="inlineStr">
-        <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250</t>
-        </is>
-      </c>
-      <c r="N104" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_filtr_mehatronika_dsg6_dq250_8386056623</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>0BH325183</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="n">
-        <v>3850</v>
-      </c>
-      <c r="D106" s="2" t="n">
-        <v>4285324155</v>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>3490</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="L106" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="inlineStr">
-        <is>
-          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
-        </is>
-      </c>
-      <c r="N106" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_dq500_dsg_7_0bh325183_4285324155</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>0BH325183</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="n">
-        <v>3850</v>
-      </c>
-      <c r="D107" s="3" t="n">
-        <v>8374830282</v>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="n">
-        <v>3850</v>
-      </c>
-      <c r="H107" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="I107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L107" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M107" s="3" t="inlineStr">
-        <is>
-          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500</t>
-        </is>
-      </c>
-      <c r="N107" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_rebristyy_mehatronika_dsg7_dq500_8374830282</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>0am325025l</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="D109" s="2" t="n">
-        <v>4444524662</v>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="n">
-        <v>1290</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J109" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K109" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L109" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="inlineStr">
-        <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
-        </is>
-      </c>
-      <c r="N109" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/porshen_vilki_mehatronika_dsg7_dq200_0am0cw_4444524662</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>0am325025l</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="D110" s="3" t="n">
-        <v>8366848631</v>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G110" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="H110" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I110" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L110" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M110" s="3" t="inlineStr">
-        <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="N110" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/porshen_tolkatel_vilki_mehatronika_dsg7_dq200_8366848631</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>0сц</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="D112" s="2" t="n">
-        <v>7260608738</v>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="n">
-        <v>450</v>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K112" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L112" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M112" s="2" t="inlineStr">
-        <is>
-          <t>Сальник толькателя мехатроника dq200 dsg7</t>
-        </is>
-      </c>
-      <c r="N112" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/salnik_tolkatelya_mehatronika_dq200_dsg7_7260608738</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>0сц</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="D113" s="3" t="n">
-        <v>8324416978</v>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G113" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="H113" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I113" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L113" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M113" s="3" t="inlineStr">
-        <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="N113" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/originalnyy_salnik_shtoka_mehatronika_dsg7_dq200_8324416978</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>0am325066ad</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>Сальник-манжета штока сцепления мехатроника DSG7</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="D115" s="2" t="n">
-        <v>4124845206</v>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="n">
-        <v>450</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L115" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M115" s="2" t="inlineStr">
-        <is>
-          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="N115" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/manzhety_salniki_mehatronika_dsg_7_dq200_0am_0cw_4124845206</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>0am325066ad</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>Сальник-манжета штока сцепления мехатроника DSG7</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="D116" s="3" t="n">
-        <v>8314644270</v>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G116" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="H116" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L116" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M116" s="3" t="inlineStr">
-        <is>
-          <t>Сальник-манжета штока сцепления мехатроника DSG7</t>
-        </is>
-      </c>
-      <c r="N116" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/salnik-manzheta_shtoka_stsepleniya_mehatronika_dsg7_8314644270</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>0AM325433E</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="D118" s="2" t="n">
-        <v>4189437762</v>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>9850</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L118" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M118" s="2" t="inlineStr">
-        <is>
-          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
-        </is>
-      </c>
-      <c r="N118" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/remkomplekt_mehatronika_dsg_7_dq200_plita_filtr_4189437762</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>0AM325433E</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="D119" s="3" t="n">
-        <v>8274692951</v>
-      </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G119" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="H119" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I119" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L119" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M119" s="3" t="inlineStr">
-        <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
-        </is>
-      </c>
-      <c r="N119" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/filtr_mehatronika_dsg7_dq200_0am325433e_8274692951</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>0am325025r</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>Усиленное опорное кольцо толкателя мехатроника</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="D121" s="2" t="n">
-        <v>4284973404</v>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="n">
-        <v>690</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K121" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L121" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M121" s="2" t="inlineStr">
-        <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
-        </is>
-      </c>
-      <c r="N121" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/usilennoe_opornoe_koltso_tolkatelya_dsg7_dq200_0am_4284973404</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>0am325025r</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>Усиленное опорное кольцо толкателя мехатроника</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="D122" s="3" t="n">
-        <v>8252362999</v>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G122" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="H122" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I122" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K122" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L122" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M122" s="3" t="inlineStr">
-        <is>
-          <t>Усиленное опорное кольцо толкателя мехатроника</t>
-        </is>
-      </c>
-      <c r="N122" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/usilennoe_opornoe_koltso_tolkatelya_mehatronika_8252362999</t>
         </is>
       </c>
     </row>

--- a/data/avito_dupes.xlsx
+++ b/data/avito_dupes.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N124"/>
+  <dimension ref="A1:N122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2496,19 +2496,19 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0am325025m-av</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Втулка (гильза) штока мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>1850</v>
+        <v>4850</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>3964711787</v>
+        <v>3965211558</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -2521,19 +2521,19 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>2890</v>
+        <v>3850</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
@@ -2542,35 +2542,35 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 новая</t>
+          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/vtulka_gilza_shtoka_mehatronika_dsg7_dq200_novaya_3964711787</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/remkomplekt_prokladki_mehatronika_dsg7_dq200_0am_3965211558</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0am325025m-av</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Втулка (гильза) штока мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1850</v>
+        <v>4850</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8349497611</v>
+        <v>8374524447</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>фид</t>
+          <t>ручное</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2579,19 +2579,19 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>1850</v>
+        <v>4350</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
@@ -2600,31 +2600,31 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>Втулка (гильза) штока мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/vtulka_gilza_shtoka_mehatronika_dsg7_dq200_8349497611</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/remkomplekt_prokladok_mehatronika_dsg7_dq200_8374524447</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0am325025m-av</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Втулка (гильза) штока мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1850</v>
+        <v>4850</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>4125069388</v>
+        <v>4125283125</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -2637,19 +2637,19 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>2990</v>
+        <v>11890</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
@@ -2658,31 +2658,31 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
+          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/gilza_mehatronika_dsg_7_dq200_0am_0cw_novaya_4125069388</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/remkomplekt_prokladki_mehatronika_dsg_7_dq200_0am_4125283125</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Втулка (гильза) штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>450</v>
+        <v>1850</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>4444712249</v>
+        <v>3964711787</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -2695,19 +2695,19 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>890</v>
+        <v>2890</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
@@ -2716,31 +2716,31 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
+          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 новая</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/maslyanyy_filtr_akpp_dsg_7_dq500_4444712249</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/vtulka_gilza_shtoka_mehatronika_dsg7_dq200_novaya_3964711787</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Втулка (гильза) штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>450</v>
+        <v>1850</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>8346375263</v>
+        <v>8349497611</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -2753,16 +2753,16 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>450</v>
+        <v>1850</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I47" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K47" s="3" t="n">
         <v>1</v>
@@ -2774,31 +2774,31 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Втулка (гильза) штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/maslyanyy_filtr_mehatronika_dsg7_dq500_0bh325183b_8346375263</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/vtulka_gilza_shtoka_mehatronika_dsg7_dq200_8349497611</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Втулка (гильза) штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>450</v>
+        <v>1850</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4316875109</v>
+        <v>4125069388</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -2811,19 +2811,19 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>890</v>
+        <v>2990</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.9</v>
+        <v>0.25</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
@@ -2832,31 +2832,31 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>Фильтр АКПП DSG 7 0BH325183B</t>
+          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/filtr_akpp_dsg_7_0bh325183b_4316875109</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/gilza_mehatronika_dsg_7_dq200_0am_0cw_novaya_4125069388</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
+          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>950</v>
+        <v>450</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>4444617509</v>
+        <v>4444712249</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -2872,16 +2872,16 @@
         <v>890</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
@@ -2890,31 +2890,31 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
+          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/bmaslyanyy_filtr_akpp_dsg6_dq250_02e305051c_4444617509</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/maslyanyy_filtr_akpp_dsg_7_dq500_4444712249</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
+          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>950</v>
+        <v>450</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>8341096851</v>
+        <v>8346375263</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -2927,16 +2927,16 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>950</v>
+        <v>450</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K51" s="3" t="n">
         <v>1</v>
@@ -2948,31 +2948,31 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
+          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/filtr_mehatronika_dsg6_dq250_02e305051c_8341096851</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/maslyanyy_filtr_mehatronika_dsg7_dq500_0bh325183b_8346375263</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
+          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>950</v>
+        <v>450</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>4317088408</v>
+        <v>4316875109</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -2981,23 +2981,23 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1490</v>
+        <v>890</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I52" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
@@ -3006,31 +3006,31 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>Фильтр DQ250 DSG 6 02E305051C</t>
+          <t>Фильтр АКПП DSG 7 0BH325183B</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/filtr_dq250_dsg_6_02e305051c_4317088408</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/filtr_akpp_dsg_7_0bh325183b_4316875109</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v>950</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>4284733993</v>
+        <v>4444617509</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -3043,19 +3043,19 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>690</v>
+        <v>890</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.45</v>
+        <v>1.3</v>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
@@ -3064,31 +3064,31 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
+          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/filtr-setka_solenoid_dl501_0b5_dsg7_n436n440_1sht_4284733993</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/bmaslyanyy_filtr_akpp_dsg6_dq250_02e305051c_4444617509</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
         <v>950</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>8294466411</v>
+        <v>8341096851</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -3104,13 +3104,13 @@
         <v>950</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K55" s="3" t="n">
         <v>1</v>
@@ -3122,31 +3122,31 @@
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/filtr-setka_solenoidov_dsg7_0b5_dl501_123014af_8294466411</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/filtr_mehatronika_dsg6_dq250_02e305051c_8341096851</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
         <v>950</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>4444869727</v>
+        <v>4317088408</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -3159,19 +3159,19 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>690</v>
+        <v>1490</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0.62</v>
+        <v>1.5</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
@@ -3180,31 +3180,31 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
+          <t>Фильтр DQ250 DSG 6 02E305051C</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/novaya_filtr_setka_na_solenoid_akpp_dsg7_0b5_dl501_4444869727</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/filtr_dq250_dsg_6_02e305051c_4317088408</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная сепараторная пластина мехатроника</t>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v>950</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>4253114863</v>
+        <v>4284733993</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -3217,19 +3217,19 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1290</v>
+        <v>690</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
@@ -3238,31 +3238,31 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
+          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/prokladki_dsg_7_separatornaya_plastina_mehatronika_4253114863</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/filtr-setka_solenoid_dl501_0b5_dsg7_n436n440_1sht_4284733993</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Оригинальная сепараторная пластина мехатроника</t>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
         <v>950</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>8286536816</v>
+        <v>8294466411</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -3278,13 +3278,13 @@
         <v>950</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K59" s="3" t="n">
         <v>1</v>
@@ -3296,31 +3296,31 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>Оригинальная сепараторная пластина мехатроника</t>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/originalnaya_separatornaya_plastina_mehatronika_8286536816</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/filtr-setka_solenoidov_dsg7_0b5_dl501_123014af_8294466411</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Оригинальная сепараторная пластина мехатроника</t>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
         <v>950</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>4445242895</v>
+        <v>4444869727</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
@@ -3329,23 +3329,23 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
         <v>690</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J60" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
@@ -3354,31 +3354,31 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
+          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/separatornaya_plastina_mehatronika_dsg7_dq200_0am_4445242895</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/novaya_filtr_setka_na_solenoid_akpp_dsg7_0b5_dl501_4444869727</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
+          <t>Оригинальная сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>5350</v>
+        <v>950</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>3965336925</v>
+        <v>4253114863</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -3391,16 +3391,16 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>3890</v>
+        <v>1290</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0.4</v>
@@ -3412,31 +3412,31 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
+          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/solenoid_mehatronika_dsg_7_dq200_bosch_regulyator_3965336925</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/prokladki_dsg_7_separatornaya_plastina_mehatronika_4253114863</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
+          <t>Оригинальная сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>5350</v>
+        <v>950</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>8232750356</v>
+        <v>8286536816</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
@@ -3449,16 +3449,16 @@
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>5350</v>
+        <v>950</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" s="3" t="n">
         <v>1</v>
@@ -3470,31 +3470,31 @@
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
+          <t>Оригинальная сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/solenoid_regulyator_davleniya_dsg7_dq200_0am325025b_8232750356</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/originalnaya_separatornaya_plastina_mehatronika_8286536816</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
+          <t>Оригинальная сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>5350</v>
+        <v>950</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>4284950339</v>
+        <v>4445242895</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -3507,19 +3507,19 @@
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>3850</v>
+        <v>690</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
@@ -3528,31 +3528,31 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/solenoid_dsg_7_dq200_0am_0cw_regulyator_davleniya_4284950339</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/separatornaya_plastina_mehatronika_dsg7_dq200_0am_4445242895</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480</t>
+          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>950</v>
+        <v>5350</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>7260747200</v>
+        <v>3965336925</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -3565,19 +3565,19 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>890</v>
+        <v>3890</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
@@ -3586,31 +3586,31 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480</t>
+          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/impulsnoe_koltso_raspredvala_gm_55565480_7260747200</t>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/solenoid_mehatronika_dsg_7_dq200_bosch_regulyator_3965336925</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480</t>
+          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>950</v>
+        <v>5350</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>8461145133</v>
+        <v>8232750356</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
@@ -3623,16 +3623,16 @@
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>950</v>
+        <v>5350</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" s="3" t="n">
         <v>1</v>
@@ -3644,2204 +3644,2158 @@
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
+          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/solenoid_regulyator_davleniya_dsg7_dq200_0am325025b_8232750356</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>0AM325025B</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>5350</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>4284950339</v>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>3850</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/solenoid_dsg_7_dq200_0am_0cw_regulyator_davleniya_4284950339</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>55565480</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>Импульсное кольцо распредвала GM 55565480</t>
         </is>
       </c>
-      <c r="N67" s="3" t="inlineStr">
+      <c r="C70" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>7260747200</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>890</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>Импульсное кольцо распредвала GM 55565480</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/impulsnoe_koltso_raspredvala_gm_55565480_7260747200</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>55565480</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Импульсное кольцо распредвала GM 55565480</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>8461145133</v>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>Импульсное кольцо распредвала GM 55565480</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/impulsnoe_koltso_raspredvala_gm_55565480_8461145133</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>0AM325587E</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
+      <c r="C73" s="2" t="n">
         <v>5850</v>
       </c>
-      <c r="D69" s="2" t="n">
+      <c r="D73" s="2" t="n">
         <v>4284880578</v>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>ручное</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="n">
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
         <v>5850</v>
       </c>
-      <c r="H69" s="2" t="n">
+      <c r="H73" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="I69" s="2" t="n">
+      <c r="I73" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J69" s="2" t="n">
+      <c r="J73" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K69" s="2" t="n">
+      <c r="K73" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="L69" s="2" t="inlineStr">
+      <c r="L73" s="2" t="inlineStr">
         <is>
           <t>ОСТАВИТЬ (привязать к фиду)</t>
         </is>
       </c>
-      <c r="M69" s="2" t="inlineStr">
+      <c r="M73" s="2" t="inlineStr">
         <is>
           <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
         </is>
       </c>
-      <c r="N69" s="2" t="inlineStr">
+      <c r="N73" s="2" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/gidroakkumulyator_dsg7_dq200_0am_0cw_original_vag_4284880578</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>0AM325587E</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал</t>
         </is>
       </c>
-      <c r="C70" s="3" t="n">
+      <c r="C74" s="3" t="n">
         <v>5850</v>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="D74" s="3" t="n">
         <v>8460910607</v>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>фид</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="n">
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n">
         <v>5850</v>
       </c>
-      <c r="H70" s="3" t="n">
+      <c r="H74" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="I70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="3" t="n">
+      <c r="I74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L70" s="3" t="inlineStr">
+      <c r="L74" s="3" t="inlineStr">
         <is>
           <t>снять</t>
         </is>
       </c>
-      <c r="M70" s="3" t="inlineStr">
+      <c r="M74" s="3" t="inlineStr">
         <is>
           <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал</t>
         </is>
       </c>
-      <c r="N70" s="3" t="inlineStr">
+      <c r="N74" s="3" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/gidroakkumulyator_mehatronika_dsg7_dq200_original_8460910607</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>0am325025С</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
+      <c r="C76" s="2" t="n">
         <v>950</v>
       </c>
-      <c r="D72" s="2" t="n">
+      <c r="D76" s="2" t="n">
         <v>4285296851</v>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>ручное</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="n">
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H72" s="2" t="n">
+      <c r="H76" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="I72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="2" t="n">
+      <c r="I76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K72" s="2" t="n">
+      <c r="K76" s="2" t="n">
         <v>0.67</v>
       </c>
-      <c r="L72" s="2" t="inlineStr">
+      <c r="L76" s="2" t="inlineStr">
         <is>
           <t>ОСТАВИТЬ (привязать к фиду)</t>
         </is>
       </c>
-      <c r="M72" s="2" t="inlineStr">
+      <c r="M76" s="2" t="inlineStr">
         <is>
           <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
-      <c r="N72" s="2" t="inlineStr">
+      <c r="N76" s="2" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/koltso_gidroakkumulyatora_dq200_dsg_7_0am_0cw_4285296851</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>0am325025С</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="C73" s="3" t="n">
+      <c r="C77" s="3" t="n">
         <v>950</v>
       </c>
-      <c r="D73" s="3" t="n">
+      <c r="D77" s="3" t="n">
         <v>8449731691</v>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>фид</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="n">
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n">
         <v>950</v>
       </c>
-      <c r="H73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="3" t="n">
+      <c r="H77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L73" s="3" t="inlineStr">
+      <c r="L77" s="3" t="inlineStr">
         <is>
           <t>снять</t>
         </is>
       </c>
-      <c r="M73" s="3" t="inlineStr">
+      <c r="M77" s="3" t="inlineStr">
         <is>
           <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="N73" s="3" t="inlineStr">
+      <c r="N77" s="3" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/koltso_gidroakkumulyatora_mehatronika_dsg7_dq200_8449731691</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>01X301127C</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
+      <c r="C79" s="2" t="n">
         <v>950</v>
       </c>
-      <c r="D75" s="2" t="n">
+      <c r="D79" s="2" t="n">
         <v>4284998704</v>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>ручное</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="n">
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
         <v>1890</v>
       </c>
-      <c r="H75" s="2" t="n">
+      <c r="H79" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="2" t="n">
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K75" s="2" t="n">
+      <c r="K79" s="2" t="n">
         <v>0.33</v>
       </c>
-      <c r="L75" s="2" t="inlineStr">
+      <c r="L79" s="2" t="inlineStr">
         <is>
           <t>ОСТАВИТЬ (привязать к фиду)</t>
         </is>
       </c>
-      <c r="M75" s="2" t="inlineStr">
+      <c r="M79" s="2" t="inlineStr">
         <is>
           <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
-      <c r="N75" s="2" t="inlineStr">
+      <c r="N79" s="2" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/bolty_mehatronika_dq200_dsg_7_0am_0cw_4284998704</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>01X301127C</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="C76" s="3" t="n">
+      <c r="C80" s="3" t="n">
         <v>950</v>
       </c>
-      <c r="D76" s="3" t="n">
+      <c r="D80" s="3" t="n">
         <v>8446880709</v>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr">
         <is>
           <t>фид</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="n">
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="n">
         <v>950</v>
       </c>
-      <c r="H76" s="3" t="n">
+      <c r="H80" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="n">
+      <c r="I80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K76" s="3" t="n">
+      <c r="K80" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L76" s="3" t="inlineStr">
+      <c r="L80" s="3" t="inlineStr">
         <is>
           <t>снять</t>
         </is>
       </c>
-      <c r="M76" s="3" t="inlineStr">
+      <c r="M80" s="3" t="inlineStr">
         <is>
           <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="N76" s="3" t="inlineStr">
+      <c r="N80" s="3" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/bolt_mehatronika_korotkiy_dsg7_dq200_0am_0cw_8446880709</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>02e305045</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Корпус масляного фильтра мехатроника DSG6 DQ250</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
+      <c r="C82" s="2" t="n">
         <v>1850</v>
       </c>
-      <c r="D78" s="2" t="n">
+      <c r="D82" s="2" t="n">
         <v>4284955885</v>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>ручное</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="n">
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="n">
         <v>1290</v>
       </c>
-      <c r="H78" s="2" t="n">
+      <c r="H82" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="I78" s="2" t="n">
+      <c r="I82" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J78" s="2" t="n">
+      <c r="J82" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K78" s="2" t="n">
+      <c r="K82" s="2" t="n">
         <v>1.33</v>
       </c>
-      <c r="L78" s="2" t="inlineStr">
+      <c r="L82" s="2" t="inlineStr">
         <is>
           <t>ОСТАВИТЬ (привязать к фиду)</t>
         </is>
       </c>
-      <c r="M78" s="2" t="inlineStr">
+      <c r="M82" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
         </is>
       </c>
-      <c r="N78" s="2" t="inlineStr">
+      <c r="N82" s="2" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_dq250_dsg_6_02e305045_4284955885</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>02e305045</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>Корпус масляного фильтра мехатроника DSG6 DQ250</t>
         </is>
       </c>
-      <c r="C79" s="3" t="n">
+      <c r="C83" s="3" t="n">
         <v>1850</v>
       </c>
-      <c r="D79" s="3" t="n">
+      <c r="D83" s="3" t="n">
         <v>8416684544</v>
       </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>фид</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="n">
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n">
         <v>1850</v>
       </c>
-      <c r="H79" s="3" t="n">
+      <c r="H83" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="I79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="n">
+      <c r="I83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K79" s="3" t="n">
+      <c r="K83" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L79" s="3" t="inlineStr">
+      <c r="L83" s="3" t="inlineStr">
         <is>
           <t>снять</t>
         </is>
       </c>
-      <c r="M79" s="3" t="inlineStr">
+      <c r="M83" s="3" t="inlineStr">
         <is>
           <t>Корпус масляного фильтра мехатроника DSG6 DQ250</t>
         </is>
       </c>
-      <c r="N79" s="3" t="inlineStr">
+      <c r="N83" s="3" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_maslyanogo_filtra_mehatronika_dsg6_dq250_8416684544</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Dq500</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
+      <c r="C85" s="2" t="n">
         <v>1850</v>
       </c>
-      <c r="D81" s="2" t="n">
+      <c r="D85" s="2" t="n">
         <v>8416432130</v>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>ручное</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>old</t>
         </is>
       </c>
-      <c r="G81" s="2" t="n">
+      <c r="G85" s="2" t="n">
         <v>1940</v>
       </c>
-      <c r="H81" s="2" t="n">
+      <c r="H85" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="2" t="n">
+      <c r="I85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="L81" s="2" t="inlineStr">
+      <c r="L85" s="2" t="inlineStr">
         <is>
           <t>ОСТАВИТЬ (привязать к фиду)</t>
         </is>
       </c>
-      <c r="M81" s="2" t="inlineStr">
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
-      <c r="N81" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_mehatronika_dsg7_dq500_0bh325183b_8416432130</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>Dq500</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
-      <c r="C82" s="3" t="n">
+      <c r="C86" s="3" t="n">
         <v>1850</v>
       </c>
-      <c r="D82" s="3" t="n">
+      <c r="D86" s="3" t="n">
         <v>8344886348</v>
       </c>
-      <c r="E82" s="3" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>фид</t>
         </is>
       </c>
-      <c r="F82" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="n">
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
         <v>1850</v>
       </c>
-      <c r="H82" s="3" t="n">
+      <c r="H86" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="I82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="3" t="n">
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L82" s="3" t="inlineStr">
+      <c r="L86" s="3" t="inlineStr">
         <is>
           <t>снять</t>
         </is>
       </c>
-      <c r="M82" s="3" t="inlineStr">
+      <c r="M86" s="3" t="inlineStr">
         <is>
           <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
-      <c r="N82" s="3" t="inlineStr">
+      <c r="N86" s="3" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_mehatronika_dsg7_dq500_0bh325183b_8344886348</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>podshipnik-vilki-6</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
+      <c r="C88" s="2" t="n">
         <v>950</v>
       </c>
-      <c r="D84" s="2" t="n">
+      <c r="D88" s="2" t="n">
         <v>4285328953</v>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>ручное</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="n">
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="n">
         <v>890</v>
       </c>
-      <c r="H84" s="2" t="n">
+      <c r="H88" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="I84" s="2" t="n">
+      <c r="I88" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J84" s="2" t="n">
+      <c r="J88" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K84" s="2" t="n">
+      <c r="K88" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="L84" s="2" t="inlineStr">
+      <c r="L88" s="2" t="inlineStr">
         <is>
           <t>ОСТАВИТЬ (привязать к фиду)</t>
         </is>
       </c>
-      <c r="M84" s="2" t="inlineStr">
+      <c r="M88" s="2" t="inlineStr">
         <is>
           <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
         </is>
       </c>
-      <c r="N84" s="2" t="inlineStr">
+      <c r="N88" s="2" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/podshipnik_vilki_dq200_dsg-7_0am_0cw_6r_4285328953</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>podshipnik-vilki-6</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
         </is>
       </c>
-      <c r="C85" s="3" t="n">
+      <c r="C89" s="3" t="n">
         <v>950</v>
       </c>
-      <c r="D85" s="3" t="n">
+      <c r="D89" s="3" t="n">
         <v>8416146322</v>
       </c>
-      <c r="E85" s="3" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>фид</t>
         </is>
       </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="n">
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n">
         <v>950</v>
       </c>
-      <c r="H85" s="3" t="n">
+      <c r="H89" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="3" t="n">
+      <c r="I89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L85" s="3" t="inlineStr">
+      <c r="L89" s="3" t="inlineStr">
         <is>
           <t>снять</t>
         </is>
       </c>
-      <c r="M85" s="3" t="inlineStr">
+      <c r="M89" s="3" t="inlineStr">
         <is>
           <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
         </is>
       </c>
-      <c r="N85" s="3" t="inlineStr">
+      <c r="N89" s="3" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/podshipnik_vilki_6-y_peredachi_i_zadnego_hoda_dsg7_8416146322</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Усиленная плита + фильтр + 2 оригинальных</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n">
+      <c r="C91" s="2" t="n">
         <v>6350</v>
       </c>
-      <c r="D87" s="2" t="n">
+      <c r="D91" s="2" t="n">
         <v>8395189204</v>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>ручное</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>old</t>
         </is>
       </c>
-      <c r="G87" s="2" t="n">
+      <c r="G91" s="2" t="n">
         <v>5950</v>
       </c>
-      <c r="H87" s="2" t="n">
+      <c r="H91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="2" t="n">
+      <c r="I91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="L87" s="2" t="inlineStr">
+      <c r="L91" s="2" t="inlineStr">
         <is>
           <t>ОСТАВИТЬ (привязать к фиду)</t>
         </is>
       </c>
-      <c r="M87" s="2" t="inlineStr">
+      <c r="M91" s="2" t="inlineStr">
         <is>
           <t>Усиленная плита + фильтр + 2 оригинальных</t>
         </is>
       </c>
-      <c r="N87" s="2" t="inlineStr">
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/usilennaya_plita_filtr_2_originalnyh_8395189204</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>Усиленная плита + фильтр + 2 оригинальных</t>
         </is>
       </c>
-      <c r="C88" s="3" t="n">
+      <c r="C92" s="3" t="n">
         <v>6350</v>
       </c>
-      <c r="D88" s="3" t="n">
+      <c r="D92" s="3" t="n">
         <v>8276249624</v>
       </c>
-      <c r="E88" s="3" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr">
         <is>
           <t>фид</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="n">
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="n">
         <v>6350</v>
       </c>
-      <c r="H88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="3" t="n">
+      <c r="H92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L88" s="3" t="inlineStr">
+      <c r="L92" s="3" t="inlineStr">
         <is>
           <t>снять</t>
         </is>
       </c>
-      <c r="M88" s="3" t="inlineStr">
+      <c r="M92" s="3" t="inlineStr">
         <is>
           <t>Усиленная плита + фильтр + 2 оригинальных</t>
         </is>
       </c>
-      <c r="N88" s="3" t="inlineStr">
+      <c r="N92" s="3" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/usilennaya_plita_filtr_2_originalnyh_8276249624</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>plita-pylniki-salniki</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
+      <c r="C94" s="2" t="n">
         <v>6350</v>
       </c>
-      <c r="D90" s="2" t="n">
+      <c r="D94" s="2" t="n">
         <v>8341832438</v>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>ручное</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>old</t>
         </is>
       </c>
-      <c r="G90" s="2" t="n">
+      <c r="G94" s="2" t="n">
         <v>6220</v>
       </c>
-      <c r="H90" s="2" t="n">
+      <c r="H94" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="2" t="n">
+      <c r="I94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="L90" s="2" t="inlineStr">
+      <c r="L94" s="2" t="inlineStr">
         <is>
           <t>ОСТАВИТЬ (привязать к фиду)</t>
         </is>
       </c>
-      <c r="M90" s="2" t="inlineStr">
+      <c r="M94" s="2" t="inlineStr">
         <is>
           <t>Прокладки + сальники + пыльники мехатроника DSG7</t>
         </is>
       </c>
-      <c r="N90" s="2" t="inlineStr">
+      <c r="N94" s="2" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/prokladki_salniki_pylniki_mehatronika_dsg7_8341832438</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>plita-pylniki-salniki</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
         </is>
       </c>
-      <c r="C91" s="3" t="n">
+      <c r="C95" s="3" t="n">
         <v>6350</v>
       </c>
-      <c r="D91" s="3" t="n">
+      <c r="D95" s="3" t="n">
         <v>8394895937</v>
       </c>
-      <c r="E91" s="3" t="inlineStr">
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>фид</t>
         </is>
       </c>
-      <c r="F91" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="n">
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="n">
         <v>6350</v>
       </c>
-      <c r="H91" s="3" t="n">
+      <c r="H95" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3" t="n">
+      <c r="I95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L91" s="3" t="inlineStr">
+      <c r="L95" s="3" t="inlineStr">
         <is>
           <t>снять</t>
         </is>
       </c>
-      <c r="M91" s="3" t="inlineStr">
+      <c r="M95" s="3" t="inlineStr">
         <is>
           <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
         </is>
       </c>
-      <c r="N91" s="3" t="inlineStr">
+      <c r="N95" s="3" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/usilennaya_gidroplita_2_pylnika_2_salnika_8394895937</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>317053TX0C</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Гидроблок вариатора JF015E 1.8л (RE0F11A)</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n">
+      <c r="C97" s="2" t="n">
         <v>32500</v>
       </c>
-      <c r="D93" s="2" t="n">
+      <c r="D97" s="2" t="n">
         <v>8387447350</v>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>ручное</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>old</t>
         </is>
       </c>
-      <c r="G93" s="2" t="n">
+      <c r="G97" s="2" t="n">
         <v>29450</v>
       </c>
-      <c r="H93" s="2" t="n">
+      <c r="H97" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="2" t="n">
+      <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="2" t="n">
         <v>0.57</v>
       </c>
-      <c r="L93" s="2" t="inlineStr">
+      <c r="L97" s="2" t="inlineStr">
         <is>
           <t>ОСТАВИТЬ (привязать к фиду)</t>
         </is>
       </c>
-      <c r="M93" s="2" t="inlineStr">
+      <c r="M97" s="2" t="inlineStr">
         <is>
           <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый</t>
         </is>
       </c>
-      <c r="N93" s="2" t="inlineStr">
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/gidroblok_variatora_jf015e_1.6l_re0f11a_novyy_8387447350</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>317053TX0C</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>Гидроблок вариатора JF015E 1.8л (RE0F11A)</t>
         </is>
       </c>
-      <c r="C94" s="3" t="n">
+      <c r="C98" s="3" t="n">
         <v>32500</v>
       </c>
-      <c r="D94" s="3" t="n">
+      <c r="D98" s="3" t="n">
         <v>8274852389</v>
       </c>
-      <c r="E94" s="3" t="inlineStr">
+      <c r="E98" s="3" t="inlineStr">
         <is>
           <t>фид</t>
         </is>
       </c>
-      <c r="F94" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="n">
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="n">
         <v>32500</v>
       </c>
-      <c r="H94" s="3" t="n">
+      <c r="H98" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="n">
+      <c r="I98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L94" s="3" t="inlineStr">
+      <c r="L98" s="3" t="inlineStr">
         <is>
           <t>снять</t>
         </is>
       </c>
-      <c r="M94" s="3" t="inlineStr">
+      <c r="M98" s="3" t="inlineStr">
         <is>
           <t>Гидроблок вариатора JF015E 1.8л (RE0F11A)</t>
         </is>
       </c>
-      <c r="N94" s="3" t="inlineStr">
+      <c r="N98" s="3" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/gidroblok_variatora_jf015e_1.8l_re0f11a_8274852389</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>DQ500</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
+      <c r="C100" s="2" t="n">
         <v>2250</v>
       </c>
-      <c r="D96" s="2" t="n">
+      <c r="D100" s="2" t="n">
         <v>4348814868</v>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>ручное</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="n">
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="n">
         <v>3490</v>
       </c>
-      <c r="H96" s="2" t="n">
+      <c r="H100" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="I96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="2" t="n">
+      <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K96" s="2" t="n">
+      <c r="K100" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="L96" s="2" t="inlineStr">
+      <c r="L100" s="2" t="inlineStr">
         <is>
           <t>ОСТАВИТЬ (привязать к фиду)</t>
         </is>
       </c>
-      <c r="M96" s="2" t="inlineStr">
+      <c r="M100" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра DQ500 DSG7</t>
         </is>
       </c>
-      <c r="N96" s="2" t="inlineStr">
+      <c r="N100" s="2" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_dq500_dsg7_4348814868</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>DQ500</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500</t>
         </is>
       </c>
-      <c r="C97" s="3" t="n">
+      <c r="C101" s="3" t="n">
         <v>2250</v>
       </c>
-      <c r="D97" s="3" t="n">
+      <c r="D101" s="3" t="n">
         <v>8387244563</v>
       </c>
-      <c r="E97" s="3" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>фид</t>
         </is>
       </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="n">
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="n">
         <v>2250</v>
       </c>
-      <c r="H97" s="3" t="n">
+      <c r="H101" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="I97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="3" t="n">
+      <c r="I101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L97" s="3" t="inlineStr">
+      <c r="L101" s="3" t="inlineStr">
         <is>
           <t>снять</t>
         </is>
       </c>
-      <c r="M97" s="3" t="inlineStr">
+      <c r="M101" s="3" t="inlineStr">
         <is>
           <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500</t>
         </is>
       </c>
-      <c r="N97" s="3" t="inlineStr">
+      <c r="N101" s="3" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_filtr_mehatronika_dsg7_dq500_8387244563</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>02E 305 045</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
+      <c r="C103" s="2" t="n">
         <v>2350</v>
       </c>
-      <c r="D99" s="2" t="n">
+      <c r="D103" s="2" t="n">
         <v>4349172359</v>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>ручное</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="n">
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="n">
         <v>1290</v>
       </c>
-      <c r="H99" s="2" t="n">
+      <c r="H103" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="I99" s="2" t="n">
+      <c r="I103" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J99" s="2" t="n">
+      <c r="J103" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K99" s="2" t="n">
+      <c r="K103" s="2" t="n">
         <v>0.62</v>
       </c>
-      <c r="L99" s="2" t="inlineStr">
+      <c r="L103" s="2" t="inlineStr">
         <is>
           <t>ОСТАВИТЬ (привязать к фиду)</t>
         </is>
       </c>
-      <c r="M99" s="2" t="inlineStr">
+      <c r="M103" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра DSG6 DQ250 02E</t>
         </is>
       </c>
-      <c r="N99" s="2" t="inlineStr">
+      <c r="N103" s="2" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_dsg6_dq250_02e_4349172359</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>02E 305 045</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250</t>
         </is>
       </c>
-      <c r="C100" s="3" t="n">
+      <c r="C104" s="3" t="n">
         <v>2350</v>
       </c>
-      <c r="D100" s="3" t="n">
+      <c r="D104" s="3" t="n">
         <v>8386056623</v>
       </c>
-      <c r="E100" s="3" t="inlineStr">
+      <c r="E104" s="3" t="inlineStr">
         <is>
           <t>фид</t>
         </is>
       </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="n">
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n">
         <v>2350</v>
       </c>
-      <c r="H100" s="3" t="n">
+      <c r="H104" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="I100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="n">
+      <c r="I104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K100" s="3" t="n">
+      <c r="K104" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L100" s="3" t="inlineStr">
+      <c r="L104" s="3" t="inlineStr">
         <is>
           <t>снять</t>
         </is>
       </c>
-      <c r="M100" s="3" t="inlineStr">
+      <c r="M104" s="3" t="inlineStr">
         <is>
           <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250</t>
         </is>
       </c>
-      <c r="N100" s="3" t="inlineStr">
+      <c r="N104" s="3" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_filtr_mehatronika_dsg6_dq250_8386056623</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>0BH325183</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра ребристый мехатроника DSG7 DQ500</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
+      <c r="C106" s="2" t="n">
         <v>3850</v>
       </c>
-      <c r="D102" s="2" t="n">
+      <c r="D106" s="2" t="n">
         <v>4285324155</v>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>ручное</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="n">
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="n">
         <v>3490</v>
       </c>
-      <c r="H102" s="2" t="n">
+      <c r="H106" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="I102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="2" t="n">
+      <c r="I106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K102" s="2" t="n">
+      <c r="K106" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="L102" s="2" t="inlineStr">
+      <c r="L106" s="2" t="inlineStr">
         <is>
           <t>ОСТАВИТЬ (привязать к фиду)</t>
         </is>
       </c>
-      <c r="M102" s="2" t="inlineStr">
+      <c r="M106" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
         </is>
       </c>
-      <c r="N102" s="2" t="inlineStr">
+      <c r="N106" s="2" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_dq500_dsg_7_0bh325183_4285324155</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>0BH325183</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>Корпус фильтра ребристый мехатроника DSG7 DQ500</t>
         </is>
       </c>
-      <c r="C103" s="3" t="n">
+      <c r="C107" s="3" t="n">
         <v>3850</v>
       </c>
-      <c r="D103" s="3" t="n">
+      <c r="D107" s="3" t="n">
         <v>8374830282</v>
       </c>
-      <c r="E103" s="3" t="inlineStr">
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>фид</t>
         </is>
       </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G103" s="3" t="n">
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="n">
         <v>3850</v>
       </c>
-      <c r="H103" s="3" t="n">
+      <c r="H107" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="I103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" s="3" t="n">
+      <c r="I107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L103" s="3" t="inlineStr">
+      <c r="L107" s="3" t="inlineStr">
         <is>
           <t>снять</t>
         </is>
       </c>
-      <c r="M103" s="3" t="inlineStr">
+      <c r="M107" s="3" t="inlineStr">
         <is>
           <t>Корпус фильтра ребристый мехатроника DSG7 DQ500</t>
         </is>
       </c>
-      <c r="N103" s="3" t="inlineStr">
+      <c r="N107" s="3" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/korpus_filtra_rebristyy_mehatronika_dsg7_dq500_8374830282</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>0am325025m</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="n"/>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n">
-        <v>4573121040</v>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>0am325025l</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>4444524662</v>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>1290</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/porshen_vilki_mehatronika_dsg7_dq200_0am0cw_4444524662</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>0am325025l</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>8366848631</v>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>фид</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="n">
-        <v>4850</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>161</v>
-      </c>
-      <c r="I105" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="K105" s="2" t="n">
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I110" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (уже из фида)</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr">
-        <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="N105" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/remkomplekt_prokladok_mehatronika_dsg7_dq200_4573121040</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>0am325025m</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="n"/>
-      <c r="C106" s="3" t="n"/>
-      <c r="D106" s="3" t="n">
-        <v>8374524447</v>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
+      <c r="J110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/porshen_tolkatel_vilki_mehatronika_dsg7_dq200_8366848631</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>0сц</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>7260608738</v>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>Сальник толькателя мехатроника dq200 dsg7</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/salnik_tolkatelya_mehatronika_dq200_dsg7_7260608738</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>0сц</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>8324416978</v>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>фид</t>
         </is>
       </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="n">
-        <v>4350</v>
-      </c>
-      <c r="H106" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="I106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="3" t="n">
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="H113" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L106" s="3" t="inlineStr">
+      <c r="L113" s="3" t="inlineStr">
         <is>
           <t>снять</t>
         </is>
       </c>
-      <c r="M106" s="3" t="inlineStr">
-        <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="N106" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/remkomplekt_prokladok_mehatronika_dsg7_dq200_8374524447</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>0am325025l</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="n">
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/originalnyy_salnik_shtoka_mehatronika_dsg7_dq200_8324416978</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>0am325066ad</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Сальник-манжета штока сцепления мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
         <v>950</v>
       </c>
-      <c r="D108" s="2" t="n">
-        <v>4444524662</v>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="D115" s="2" t="n">
+        <v>4124845206</v>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>ручное</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="n">
-        <v>1290</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J108" s="2" t="n">
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/manzhety_salniki_mehatronika_dsg_7_dq200_0am_0cw_4124845206</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>0am325066ad</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>Сальник-манжета штока сцепления мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>8314644270</v>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>Сальник-манжета штока сцепления мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/salnik-manzheta_shtoka_stsepleniya_mehatronika_dsg7_8314644270</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>0AM325433E</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>4189437762</v>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>9850</v>
+      </c>
+      <c r="H118" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K108" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L108" s="2" t="inlineStr">
+      <c r="I118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
         <is>
           <t>ОСТАВИТЬ (привязать к фиду)</t>
         </is>
       </c>
-      <c r="M108" s="2" t="inlineStr">
-        <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
-        </is>
-      </c>
-      <c r="N108" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/porshen_vilki_mehatronika_dsg7_dq200_0am0cw_4444524662</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>0am325025l</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="n">
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/remkomplekt_mehatronika_dsg_7_dq200_plita_filtr_4189437762</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>0AM325433E</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="n">
         <v>950</v>
       </c>
-      <c r="D109" s="3" t="n">
-        <v>8366848631</v>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
+      <c r="D119" s="3" t="n">
+        <v>8274692951</v>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>фид</t>
         </is>
       </c>
-      <c r="F109" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="n">
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="n">
         <v>950</v>
       </c>
-      <c r="H109" s="3" t="n">
+      <c r="H119" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I109" s="3" t="n">
+      <c r="I119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J109" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="3" t="n">
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>снять</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/filtr_mehatronika_dsg7_dq200_0am325433e_8274692951</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>0am325025r</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Усиленное опорное кольцо толкателя мехатроника</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>4284973404</v>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>690</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>ОСТАВИТЬ (привязать к фиду)</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/usilennoe_opornoe_koltso_tolkatelya_dsg7_dq200_0am_4284973404</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>0am325025r</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Усиленное опорное кольцо толкателя мехатроника</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>8252362999</v>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>фид</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L109" s="3" t="inlineStr">
+      <c r="K122" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
         <is>
           <t>снять</t>
         </is>
       </c>
-      <c r="M109" s="3" t="inlineStr">
-        <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="N109" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/porshen_tolkatel_vilki_mehatronika_dsg7_dq200_8366848631</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>0сц</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="D111" s="2" t="n">
-        <v>7260608738</v>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="n">
-        <v>450</v>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K111" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L111" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M111" s="2" t="inlineStr">
-        <is>
-          <t>Сальник толькателя мехатроника dq200 dsg7</t>
-        </is>
-      </c>
-      <c r="N111" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/salnik_tolkatelya_mehatronika_dq200_dsg7_7260608738</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>0сц</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="D112" s="3" t="n">
-        <v>8324416978</v>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G112" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="H112" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I112" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L112" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M112" s="3" t="inlineStr">
-        <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="N112" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/originalnyy_salnik_shtoka_mehatronika_dsg7_dq200_8324416978</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>0am325066ad</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Сальник-манжета штока сцепления мехатроника DSG7</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="D114" s="2" t="n">
-        <v>4124845206</v>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="n">
-        <v>450</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K114" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L114" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M114" s="2" t="inlineStr">
-        <is>
-          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="N114" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/manzhety_salniki_mehatronika_dsg_7_dq200_0am_0cw_4124845206</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>0am325066ad</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>Сальник-манжета штока сцепления мехатроника DSG7</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="D115" s="3" t="n">
-        <v>8314644270</v>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G115" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="H115" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L115" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M115" s="3" t="inlineStr">
-        <is>
-          <t>Сальник-манжета штока сцепления мехатроника DSG7</t>
-        </is>
-      </c>
-      <c r="N115" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/salnik-manzheta_shtoka_stsepleniya_mehatronika_dsg7_8314644270</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>0AM325433E</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>4189437762</v>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>9850</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L117" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M117" s="2" t="inlineStr">
-        <is>
-          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
-        </is>
-      </c>
-      <c r="N117" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/remkomplekt_mehatronika_dsg_7_dq200_plita_filtr_4189437762</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>0AM325433E</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="D118" s="3" t="n">
-        <v>8274692951</v>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="H118" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I118" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L118" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M118" s="3" t="inlineStr">
-        <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
-        </is>
-      </c>
-      <c r="N118" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/filtr_mehatronika_dsg7_dq200_0am325433e_8274692951</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>0am325025r</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="M122" s="3" t="inlineStr">
         <is>
           <t>Усиленное опорное кольцо толкателя мехатроника</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="D120" s="2" t="n">
-        <v>4284973404</v>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="n">
-        <v>690</v>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K120" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L120" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M120" s="2" t="inlineStr">
-        <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
-        </is>
-      </c>
-      <c r="N120" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/usilennoe_opornoe_koltso_tolkatelya_dsg7_dq200_0am_4284973404</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>0am325025r</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>Усиленное опорное кольцо толкателя мехатроника</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="D121" s="3" t="n">
-        <v>8252362999</v>
-      </c>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>фид</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G121" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="H121" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I121" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K121" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L121" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M121" s="3" t="inlineStr">
-        <is>
-          <t>Усиленное опорное кольцо толкателя мехатроника</t>
-        </is>
-      </c>
-      <c r="N121" s="3" t="inlineStr">
+      <c r="N122" s="3" t="inlineStr">
         <is>
           <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/usilennoe_opornoe_koltso_tolkatelya_mehatronika_8252362999</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>0am325025m-av</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="n">
-        <v>4850</v>
-      </c>
-      <c r="D123" s="2" t="n">
-        <v>3965211558</v>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="n">
-        <v>3850</v>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K123" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>ОСТАВИТЬ (привязать к фиду)</t>
-        </is>
-      </c>
-      <c r="M123" s="2" t="inlineStr">
-        <is>
-          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
-        </is>
-      </c>
-      <c r="N123" s="2" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/remkomplekt_prokladki_mehatronika_dsg7_dq200_0am_3965211558</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>0am325025m-av</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="n">
-        <v>4850</v>
-      </c>
-      <c r="D124" s="3" t="n">
-        <v>4125283125</v>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G124" s="3" t="n">
-        <v>11890</v>
-      </c>
-      <c r="H124" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="I124" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L124" s="3" t="inlineStr">
-        <is>
-          <t>снять</t>
-        </is>
-      </c>
-      <c r="M124" s="3" t="inlineStr">
-        <is>
-          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
-        </is>
-      </c>
-      <c r="N124" s="3" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/moskva/zapchasti_i_aksessuary/remkomplekt_prokladki_mehatronika_dsg_7_dq200_0am_4125283125</t>
         </is>
       </c>
     </row>
